--- a/data/trans_orig/IP16B08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B08-Clase-trans_orig.xlsx
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28952</t>
+          <t>29171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
